--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/6913-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/6913-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9CAAE646-DEB3-472B-831E-9245D3A914B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6E8B8005-3E28-4239-B7BF-80A4919CC07B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{7971534A-0763-473B-B7AD-E4A98056CB85}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{2B39C6B9-FF8E-4077-9C58-73CEA8121166}"/>
   </bookViews>
   <sheets>
     <sheet name="6913-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1397,24 +1397,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91101852-FCA8-4591-B695-514601630232}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10EA810B-9C88-494D-BF08-F2E2EED4D6C7}">
   <dimension ref="A1:R9"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="11.77734375" customWidth="1"/>
-    <col min="3" max="3" width="7.33203125" customWidth="1"/>
-    <col min="4" max="4" width="7.6640625" customWidth="1"/>
-    <col min="5" max="5" width="7.33203125" customWidth="1"/>
-    <col min="6" max="7" width="7.6640625" customWidth="1"/>
-    <col min="8" max="8" width="7.33203125" customWidth="1"/>
-    <col min="9" max="10" width="7.6640625" customWidth="1"/>
-    <col min="11" max="13" width="7.33203125" customWidth="1"/>
-    <col min="14" max="14" width="7.6640625" customWidth="1"/>
-    <col min="15" max="17" width="7.33203125" customWidth="1"/>
-    <col min="18" max="18" width="8" customWidth="1"/>
+    <col min="1" max="2" width="16.25" customWidth="1"/>
+    <col min="3" max="3" width="9" customWidth="1"/>
+    <col min="4" max="4" width="9.5" customWidth="1"/>
+    <col min="5" max="5" width="9" customWidth="1"/>
+    <col min="6" max="7" width="9.5" customWidth="1"/>
+    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="9" max="10" width="9.5" customWidth="1"/>
+    <col min="11" max="13" width="9" customWidth="1"/>
+    <col min="14" max="14" width="9.5" customWidth="1"/>
+    <col min="15" max="17" width="9" customWidth="1"/>
+    <col min="18" max="18" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
@@ -1442,7 +1442,7 @@
       <c r="Q1" s="26"/>
       <c r="R1" s="18"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="19" t="s">
         <v>1</v>
       </c>
@@ -1472,7 +1472,7 @@
       <c r="Q2" s="28"/>
       <c r="R2" s="29"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
         <v>2</v>
       </c>
@@ -1518,7 +1518,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="21"/>
       <c r="B4" s="22"/>
       <c r="C4" s="7"/>
@@ -1568,7 +1568,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="33">
         <v>2025</v>
       </c>
@@ -1622,7 +1622,7 @@
         <v>1.86</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="35">
         <v>2024</v>
       </c>
@@ -1676,7 +1676,7 @@
         <v>1.9</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="33">
         <v>2023</v>
       </c>
@@ -1730,7 +1730,7 @@
         <v>5.12</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="35">
         <v>2022</v>
       </c>
@@ -1784,7 +1784,7 @@
         <v>2.52</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="33" t="s">
         <v>25</v>
       </c>
